--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -294,9 +294,6 @@
     <t xml:space="preserve">test station issue? </t>
   </si>
   <si>
-    <t>change test station and retest it again.</t>
-  </si>
-  <si>
     <t>6a89dc65</t>
   </si>
   <si>
@@ -573,6 +570,20 @@
   </si>
   <si>
     <t>1.Check the log and find the error windu. 2.Try to swap windu and test it again(OE team) 3. If the swap still fails and the connection ports are the same, please perform a hardware check.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change test station and retest it again.
+1.機器背後電源線插到底
+2.BMC是否有log
+3.如果BMC沒有開機=&gt;12V_AUX是否有短路
+4.LED燈是否全亮不會滅?(LEDcable受傷:TS2#8
+5.BMC是否完全沒有checkpoint=&gt;CSM重跑jtag
+6.12V_main是否短路(csm/mgmt LED燈號只有一半)
+7.四個busbar拆開是否短路
+8.確認是否FBK鎖上以後短路
+9.BMC是否停在check point 15=&gt;換MGMT,DDR
+10.Console 是否有Failed to start ntpsec.service =&gt;測站問題</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1302,7 +1313,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15">
+    <row r="13" spans="1:11" ht="165">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1318,8 +1329,8 @@
       <c r="G13" t="s">
         <v>71</v>
       </c>
-      <c r="H13" t="s">
-        <v>72</v>
+      <c r="H13" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15">
@@ -1330,22 +1341,22 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
         <v>73</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>76</v>
-      </c>
-      <c r="H14" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15">
@@ -1356,22 +1367,22 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" t="s">
         <v>78</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>81</v>
-      </c>
-      <c r="H15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15">
@@ -1382,25 +1393,25 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" t="s">
         <v>83</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>84</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" t="s">
+        <v>81</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15">
@@ -1411,20 +1422,20 @@
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
         <v>87</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>88</v>
       </c>
-      <c r="E17" t="s">
-        <v>89</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" s="5"/>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15">
@@ -1435,103 +1446,103 @@
         <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
         <v>91</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>92</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>94</v>
-      </c>
-      <c r="H18" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" t="s">
         <v>97</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>98</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G19" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="J19" t="s">
         <v>100</v>
-      </c>
-      <c r="J19" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
         <v>102</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>103</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
         <v>104</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>105</v>
-      </c>
-      <c r="H20" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="G21" t="s">
         <v>36</v>
       </c>
       <c r="H21" t="s">
+        <v>110</v>
+      </c>
+      <c r="J21" t="s">
         <v>111</v>
-      </c>
-      <c r="J21" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15">
@@ -1539,40 +1550,40 @@
         <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G22" t="s">
         <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15"/>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
         <v>115</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>116</v>
       </c>
-      <c r="E24" t="s">
-        <v>117</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15">
@@ -1583,22 +1594,22 @@
         <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" t="s">
         <v>118</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>119</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" t="s">
         <v>120</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>121</v>
-      </c>
-      <c r="H25" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15">
@@ -1606,16 +1617,16 @@
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
         <v>123</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" t="s">
         <v>124</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H26" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15">
@@ -1623,13 +1634,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>127</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15">
@@ -1637,19 +1648,19 @@
         <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" t="s">
         <v>128</v>
       </c>
-      <c r="D28" t="s">
-        <v>129</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15">
@@ -1657,16 +1668,16 @@
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" t="s">
         <v>130</v>
       </c>
-      <c r="D29" t="s">
-        <v>131</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15">
@@ -1674,19 +1685,19 @@
         <v>11</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" t="s">
         <v>132</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>133</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" t="s">
         <v>134</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G30" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15">
@@ -1697,22 +1708,22 @@
         <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" t="s">
         <v>136</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E31" t="s">
-        <v>134</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H31" s="5" t="s">
+      <c r="J31" t="s">
         <v>138</v>
-      </c>
-      <c r="J31" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15">
@@ -1723,25 +1734,25 @@
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" t="s">
         <v>140</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>141</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G32" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="H32" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="J32" t="s">
         <v>144</v>
-      </c>
-      <c r="J32" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="15">
@@ -1749,19 +1760,19 @@
         <v>11</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" t="s">
         <v>146</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="H34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="15">
@@ -1769,56 +1780,56 @@
         <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" t="s">
         <v>149</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F35" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="H35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="15">
       <c r="B37" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" t="s">
         <v>153</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G37" t="s">
         <v>154</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>155</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" t="s">
         <v>156</v>
-      </c>
-      <c r="J37" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="15">
       <c r="B38" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -959,7 +959,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1842,6 +1842,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9191A586FB6BF428DA6CE3AFBC36CC2" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="93226386e723f3eec884d41ea14434fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9" xmlns:ns3="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e82c8add95932482acff31e34b978d29" ns2:_="" ns3:_="">
     <xsd:import namespace="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
@@ -2048,27 +2068,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE2B39F-8B1E-434F-AA50-190A864E0746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5"/>
+    <ds:schemaRef ds:uri="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0207815-F4C9-4B0B-8379-8B1E5F301B50}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B80DCE0-1924-49A6-B8F1-3B71CC84536B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2087,25 +2106,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0207815-F4C9-4B0B-8379-8B1E5F301B50}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE2B39F-8B1E-434F-AA50-190A864E0746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5"/>
-    <ds:schemaRef ds:uri="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{44ccf059-af5d-4b92-932d-3690a1231c55}" enabled="1" method="Standard" siteId="{cb3d8dcd-2ed2-4bad-89a5-e0a7195fb643}" removed="0"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="165">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -198,12 +198,6 @@
     <t>6727cc66</t>
   </si>
   <si>
-    <t>mgmt_system_gpio-system_gpio_cplds_without_test_mode-FAIL-MEASUREMENT</t>
-  </si>
-  <si>
-    <t>change the test stataion, NV will remove this test item ??</t>
-  </si>
-  <si>
     <t>6d8b7986</t>
   </si>
   <si>
@@ -244,12 +238,6 @@
   </si>
   <si>
     <t>write_i2c_block' function failed: device=/dev/mst/192.168.10.20:23108, @dev@mst@dev-i2c-15, i2c_addr=0x70, addr_width=1, reg_addr=0x0, size=2</t>
-  </si>
-  <si>
-    <t>Fiber prbs issue</t>
-  </si>
-  <si>
-    <t>NV debugging, SA090057 has a special version test.</t>
   </si>
   <si>
     <t>(EVT#8)</t>
@@ -510,9 +498,6 @@
   </si>
   <si>
     <t>temperature issue</t>
-  </si>
-  <si>
-    <t>HW check ??</t>
   </si>
   <si>
     <t>(EVT#16)</t>
@@ -586,12 +571,50 @@
 10.Console 是否有Failed to start ntpsec.service =&gt;測站問題</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>如果是csm MPS29816 溫度過高, 通知ME
+re-curing 20min, 冷卻30min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mgmt_system_gpio-system_gpio_cplds_without_test_mode-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mnb_cpld_main_i2c__reg_BOARD_INT_STAT_REG_2__BIT_SMB_ALERT_L-DPL mnb_cpld_main_i2c, Register BOARD_INT_STAT_REG_2, bit SMB_ALERT_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change the test stataion, NV will remove this test item ??
+Retest
+(客人說是超過70度的原因 但檢查溫度沒有看出來 目前這項軟體認為不需要在FT測試這個 他們會討論移除這個項目)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fiber prbs issue
+TS2 MPS是0x70 (0x60~0x6C, 0x70, 0x71, 0x72) 但是test program卻要偵測0x6d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NV debugging, SA090057 has a special version test.
+Change station and  restest it again.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csm1_els_brd_cpld_reg_ft_prsnt_fnm__bit_fnm_prsnt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fnm module issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,6 +634,13 @@
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="3">
@@ -639,7 +669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -653,6 +683,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -959,7 +992,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1151,7 +1184,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15">
+    <row r="7" spans="1:11" ht="60">
       <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1159,7 +1192,10 @@
         <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>158</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>39</v>
@@ -1167,8 +1203,8 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" t="s">
-        <v>41</v>
+      <c r="H7" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15">
@@ -1179,22 +1215,22 @@
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
         <v>42</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" t="s">
         <v>43</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>44</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15">
@@ -1205,28 +1241,28 @@
         <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>50</v>
       </c>
-      <c r="H9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15">
+    </row>
+    <row r="10" spans="1:11" ht="45">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1234,25 +1270,25 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J10" t="s">
         <v>54</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15">
@@ -1263,54 +1299,54 @@
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
+      <c r="I11" t="s">
         <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15">
       <c r="A12" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="J12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="165">
@@ -1318,19 +1354,19 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15">
@@ -1341,22 +1377,22 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
         <v>72</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15">
@@ -1367,22 +1403,22 @@
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" t="s">
         <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" t="s">
-        <v>80</v>
-      </c>
-      <c r="H15" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15">
@@ -1393,25 +1429,25 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15">
@@ -1422,20 +1458,20 @@
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H17" s="5"/>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15">
@@ -1446,103 +1482,103 @@
         <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" t="s">
         <v>90</v>
-      </c>
-      <c r="D18" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" t="s">
-        <v>93</v>
-      </c>
-      <c r="H18" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15">
       <c r="A19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="J19" t="s">
         <v>96</v>
-      </c>
-      <c r="D19" t="s">
-        <v>97</v>
-      </c>
-      <c r="E19" t="s">
-        <v>98</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" t="s">
-        <v>99</v>
-      </c>
-      <c r="J19" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15">
       <c r="A20" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" t="s">
         <v>101</v>
-      </c>
-      <c r="D20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15">
       <c r="A21" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G21" t="s">
         <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15">
@@ -1550,40 +1586,40 @@
         <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G22" t="s">
         <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="J22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15"/>
     <row r="24" spans="1:10" ht="15">
       <c r="A24" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15">
@@ -1594,22 +1630,22 @@
         <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" t="s">
         <v>117</v>
-      </c>
-      <c r="D25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" t="s">
-        <v>119</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15">
@@ -1617,16 +1653,22 @@
         <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>119</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15">
@@ -1634,13 +1676,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15">
@@ -1648,19 +1690,19 @@
         <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15">
@@ -1668,16 +1710,16 @@
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H29" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15">
@@ -1685,19 +1727,19 @@
         <v>11</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G30" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15">
@@ -1708,25 +1750,25 @@
         <v>11</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E31" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>137</v>
-      </c>
       <c r="J31" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="15">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="30">
       <c r="A32" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,25 +1776,25 @@
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" t="s">
+        <v>138</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J32" t="s">
         <v>139</v>
-      </c>
-      <c r="D32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" t="s">
-        <v>141</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G32" t="s">
-        <v>142</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="J32" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="15">
@@ -1760,19 +1802,19 @@
         <v>11</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H34" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="15">
@@ -1780,56 +1822,56 @@
         <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H35" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="15">
       <c r="B37" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" t="s">
+        <v>148</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H37" t="s">
+        <v>150</v>
+      </c>
+      <c r="J37" t="s">
         <v>151</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37" t="s">
-        <v>153</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G37" t="s">
-        <v>154</v>
-      </c>
-      <c r="H37" t="s">
-        <v>155</v>
-      </c>
-      <c r="J37" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="15">
       <c r="B38" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1842,26 +1884,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9191A586FB6BF428DA6CE3AFBC36CC2" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="93226386e723f3eec884d41ea14434fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9" xmlns:ns3="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e82c8add95932482acff31e34b978d29" ns2:_="" ns3:_="">
     <xsd:import namespace="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
@@ -2068,26 +2090,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE2B39F-8B1E-434F-AA50-190A864E0746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5"/>
-    <ds:schemaRef ds:uri="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0207815-F4C9-4B0B-8379-8B1E5F301B50}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B80DCE0-1924-49A6-B8F1-3B71CC84536B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2106,6 +2129,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0207815-F4C9-4B0B-8379-8B1E5F301B50}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE2B39F-8B1E-434F-AA50-190A864E0746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5"/>
+    <ds:schemaRef ds:uri="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{44ccf059-af5d-4b92-932d-3690a1231c55}" enabled="1" method="Standard" siteId="{cb3d8dcd-2ed2-4bad-89a5-e0a7195fb643}" removed="0"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="171">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -385,9 +385,6 @@
   </si>
   <si>
     <t>SA092557</t>
-  </si>
-  <si>
-    <t>320d1675</t>
   </si>
   <si>
     <t>bmc_burn_if_needed-check_bmc_format_and_version_and_burn_if_wrong_chameleon_bmc</t>
@@ -477,9 +474,6 @@
   </si>
   <si>
     <t>385c370a</t>
-  </si>
-  <si>
-    <t>csm_monitoring_under_stress-get_els_pemi_laser_source_advanced-ERROR-ValueError</t>
   </si>
   <si>
     <t>OE team check ??</t>
@@ -609,12 +603,45 @@
     <t>fnm module issue</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>csm_monitoring_under_stress-get_els_pemi_laser_source_advanced-ERROR-ValueError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.檢查是否op 沒有按/或機台問題
+2.檢查LED cable是否有受損 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(TS2#30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>567e5ee0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reset button issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_pb_pushed-Verify group_pb button pushed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(TS2#89)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -641,6 +668,14 @@
       <name val="Aptos Narrow"/>
       <family val="1"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -672,19 +707,25 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1003,23 +1044,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.375" style="1" customWidth="1"/>
     <col min="2" max="3" width="14.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="92.125" customWidth="1"/>
-    <col min="5" max="5" width="151.625" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="58.75" customWidth="1"/>
-    <col min="8" max="8" width="64.875" customWidth="1"/>
-    <col min="9" max="9" width="106.375" customWidth="1"/>
-    <col min="10" max="10" width="39.25" customWidth="1"/>
-    <col min="11" max="11" width="28.375" customWidth="1"/>
-    <col min="12" max="12" width="36.625" customWidth="1"/>
+    <col min="4" max="4" width="87.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="151.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="58.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="64.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="106.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="39.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="36.625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1" spans="1:10" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,600 +1070,492 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15">
+    <row r="2" spans="1:10" ht="15">
       <c r="A2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15">
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="B4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="15">
-      <c r="A3" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15">
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="60">
+      <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15">
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="45">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="165">
+      <c r="B13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
+      <c r="A16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="A17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15">
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
+      <c r="B20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="H21" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15">
-      <c r="A4" s="1" t="s">
+    <row r="22" spans="1:9" ht="15">
+      <c r="B22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15">
+      <c r="A23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15">
+      <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F24" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H6" t="s">
+      <c r="G24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I6" t="s">
+      <c r="H24" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="60">
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15">
-      <c r="A12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="165">
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15">
-      <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="15">
-      <c r="A16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="5"/>
-      <c r="J17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15">
-      <c r="A18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G18" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15">
-      <c r="A19" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G19" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15">
-      <c r="A20" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G20" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15">
-      <c r="A21" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" t="s">
-        <v>106</v>
-      </c>
-      <c r="J21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15">
-      <c r="B22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" t="s">
-        <v>106</v>
-      </c>
-      <c r="J22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15"/>
-    <row r="24" spans="1:10" ht="15">
-      <c r="A24" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15">
+    <row r="25" spans="1:9" ht="15">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -1630,251 +1563,285 @@
         <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" t="s">
-        <v>115</v>
+        <v>45</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G25" t="s">
-        <v>116</v>
-      </c>
-      <c r="H25" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15">
+        <v>48</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15">
+      <c r="A26" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="B26" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>163</v>
+        <v>24</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H26" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15">
+      <c r="A27" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="B27" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>122</v>
+        <v>24</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15">
+        <v>27</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15">
+      <c r="A28" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" t="s">
-        <v>124</v>
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="G28" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15">
+      <c r="A29" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D29" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="I29" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15">
+      <c r="B30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="15">
-      <c r="B30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" t="s">
-        <v>129</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="G30" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15">
+      <c r="I30" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="30">
       <c r="A31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30">
+      <c r="A32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15">
+      <c r="A33" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" t="s">
-        <v>132</v>
-      </c>
-      <c r="E31" t="s">
-        <v>129</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="J31" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="30">
-      <c r="A32" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15">
+      <c r="A34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15">
+      <c r="A35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D32" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G32" t="s">
-        <v>138</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J32" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" ht="15">
-      <c r="B34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" t="s">
-        <v>141</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="H34" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" ht="15">
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H35" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" ht="15">
-      <c r="B37" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G37" t="s">
-        <v>149</v>
-      </c>
-      <c r="H37" t="s">
-        <v>150</v>
-      </c>
-      <c r="J37" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" ht="15">
-      <c r="B38" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>127</v>
+        <v>51</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15">
+      <c r="A36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:J36">
+    <sortCondition ref="D1"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions headings="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="176">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -424,9 +424,6 @@
   </si>
   <si>
     <t>suspect the windu issue</t>
-  </si>
-  <si>
-    <t>suspect a windu issue, replace the windu and test again. (identify which windu is faulty), NV already resolve</t>
   </si>
   <si>
     <t>562eSf9e</t>
@@ -464,9 +461,6 @@
     <t>8ffcfa5e</t>
   </si>
   <si>
-    <t>csm_monitoring_under_stress-get_pemi_module_status-ERROR-ValueError</t>
-  </si>
-  <si>
     <t>status returned error code 7</t>
   </si>
   <si>
@@ -537,18 +531,11 @@
     <t>(6M BU#4-3)</t>
   </si>
   <si>
-    <t>csm_monitoring under stress-get-pemi_moudle_status-ERROR-ValueError</t>
-  </si>
-  <si>
     <t>320d1675</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>OE issue and OE team check</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.Check the log and find the error windu. 2.Try to swap windu and test it again(OE team) 3. If the swap still fails and the connection ports are the same, please perform a hardware check.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -636,12 +623,48 @@
     <t>(TS2#89)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>csm_monitoring_under_stress-get_pemi_module_status-ERROR-ValueError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Check the log and find the error windu. 
+2.Try to swap windu and test it again(OE team) 
+3. If the swap still fails and the connection ports are the same, please perform a hardware check.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replace the windu and test again. (identify which windu is faulty), NV already resolve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify fw burn comex-verify fw burn ERROR-TimeoutError</t>
+  </si>
+  <si>
+    <t>bec3c5db</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubProcess execution has exceeded timeout limit: 1200 sec​</t>
+  </si>
+  <si>
+    <t>windu issue, no els input power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_62065109160010 (BU#36)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Replace windu and check els input power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,6 +700,21 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -704,7 +742,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -727,6 +765,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1052,7 +1092,7 @@
     <col min="4" max="4" width="87.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="151.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="58.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="64.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="86.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="106.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="28.375" style="1" customWidth="1"/>
@@ -1100,7 +1140,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>103</v>
@@ -1123,7 +1163,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>107</v>
@@ -1139,80 +1179,80 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B4" s="1" t="s">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>150</v>
+      <c r="G4" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="60">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="60">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>137</v>
+        <v>119</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
@@ -1220,33 +1260,45 @@
         <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15">
+        <v>116</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="45">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="45">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -1254,19 +1306,19 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15">
@@ -1277,65 +1329,59 @@
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="165">
       <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>142</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="45">
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="165">
-      <c r="B13" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>149</v>
+      <c r="G13" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15">
@@ -1343,33 +1389,33 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15">
+      <c r="A15" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>152</v>
+        <v>110</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15">
@@ -1380,36 +1426,42 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>94</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15">
-      <c r="A17" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="B17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>93</v>
+        <v>163</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>95</v>
+        <v>164</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>96</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1417,22 +1469,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>166</v>
+        <v>123</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1440,145 +1483,154 @@
         <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>125</v>
+        <v>140</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15">
+      <c r="B21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="15">
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15">
-      <c r="A21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>21</v>
+        <v>153</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15">
+      <c r="A22" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>156</v>
+        <v>69</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>158</v>
+        <v>71</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>72</v>
+        <v>37</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1592,39 +1644,39 @@
         <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1635,65 +1687,68 @@
         <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>16</v>
+        <v>84</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="I28" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15">
-      <c r="A29" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" s="4"/>
+        <v>66</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="I29" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="30">
+      <c r="A30" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="B30" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>170</v>
+        <v>58</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="30">
       <c r="A31" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>11</v>
@@ -1708,114 +1763,111 @@
         <v>57</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="30">
+        <v>63</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="15">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="45">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>101</v>
+        <v>52</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15">
+        <v>41</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="14.25" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>10</v>
       </c>
@@ -1823,19 +1875,22 @@
         <v>11</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>42</v>
+        <v>171</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>43</v>
+        <v>173</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>44</v>
+        <v>175</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="188">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -657,6 +657,53 @@
   </si>
   <si>
     <t>Replace windu and check els input power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA092538</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07d86568</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mgmt_cpu_monitoring_under_stress-read_cpu_temperatures-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cpu_temperature_core_0-checking CPU temperature core 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expected: 10 &lt;= x &lt;= 67, Received:100.0</t>
+  </si>
+  <si>
+    <t>if temperature = 100 then change test station and report case to TE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f7340a0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset_button-reset_test-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset_pushed-Verify reset button pushed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check if press the reset button or not</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Check if the reset button works correctly. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63765151110010</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1084,7 +1131,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.375" style="1" customWidth="1"/>
@@ -1516,121 +1563,124 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
+      <c r="A21" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="B21" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15">
+      <c r="B22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15">
-      <c r="A22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15">
       <c r="A23" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
       <c r="A24" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15">
       <c r="A25" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15">
@@ -1644,39 +1694,39 @@
         <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15">
       <c r="A27" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1687,68 +1737,65 @@
         <v>11</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15">
+      <c r="A29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="I28" s="1" t="s">
+      <c r="G29" s="4"/>
+      <c r="I29" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15">
-      <c r="B29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="1" t="s">
+    <row r="30" spans="1:9" ht="30">
+      <c r="B30" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="30">
-      <c r="A30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="30">
       <c r="A31" s="1" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>11</v>
@@ -1763,138 +1810,190 @@
         <v>57</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>90</v>
+        <v>63</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
       <c r="A33" s="1" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="45">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>54</v>
+        <v>98</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="14.25" customHeight="1">
       <c r="A36" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A37" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="B37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D38" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E38" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I38" s="9" t="s">
         <v>174</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:J36">
+  <sortState ref="A2:J38">
     <sortCondition ref="D1"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="188">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -1265,7 +1265,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="60">
+    <row r="6" spans="1:10" ht="25.2" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="45">
+    <row r="9" spans="1:10" ht="22.8" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1782,6 +1782,9 @@
       </c>
       <c r="D30" s="1" t="s">
         <v>66</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>67</v>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="201">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -189,9 +189,6 @@
     <t>test station issue</t>
   </si>
   <si>
-    <t>if temperature = 100 then change test station and report case to TE</t>
-  </si>
-  <si>
     <t>Expected: 10 &lt;= x &lt;= 65, Received: 100.0</t>
   </si>
   <si>
@@ -262,15 +259,6 @@
   </si>
   <si>
     <t>SA090038</t>
-  </si>
-  <si>
-    <t>power light isn't on and minicom also no responds</t>
-  </si>
-  <si>
-    <t>Let hardware engineer check the power path, the cable connecting the MGMT module to the PDB was not fully seated.</t>
-  </si>
-  <si>
-    <t>SN_63665151890012 (TS2#77)</t>
   </si>
   <si>
     <t>c1444446</t>
@@ -679,10 +667,6 @@
     <t>Expected: 10 &lt;= x &lt;= 67, Received:100.0</t>
   </si>
   <si>
-    <t>if temperature = 100 then change test station and report case to TE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>f7340a0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -704,6 +688,92 @@
   </si>
   <si>
     <t>SN_63765151110010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (localhost login:)|(ONIE: Rescue Mode ...)|(sonic login:)|(ONIE: OS Install Mode ...)
+Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (GNU GRUB)|(ONIE: Rescue Mode ...)|(Start PXE over)|(ONIE: OS Install Mode ...)|(Secure Boot Violation)|(Access granted)
+Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (Secure Boot Violation)|(ONIE: Rescue Mode ...)|(Access granted)|(Start PXE over)|(ONIE: OS Install Mode ...)|(GNU GRUB)
+Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (GNU GRUB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pcie_errors_check_before_stress-x86_pcie_capability_check-FAIL-MEASUREMENT;</t>
+  </si>
+  <si>
+    <t>mst_devices_Linkx-MST Linkx device presence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63265143660004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03784b04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NV issue, follow instruction by Sharon
+(Before) step by step 5 times still Gen1x4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if temperature = 100 then change test station (retest)
+still fail and then report case to TE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. power light isn't on and minicom also no responds
+2. BMC no console.During disassembly of the MGMT, it was discovered that the MGMT-to-PBD cable was not fully seated.
+3. Check cable between IO board &amp; LED board damaged. Causing 3v3_aux shorted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Let hardware engineer check the power path, the cable connecting the MGMT module to the PDB was not fully seated.
+2. Change new cable and IO board 
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63665151890012 (TS2#77)
+SN_63265142450009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setpoints_overall_flow_rate_sp_lpm-canonical setpoint overall_flow_rate_sp_lpm check (expected 30.0 ±5.0%)
+setpoints_overall_temperature_sp_c-canonical setpoint overall_temperature_sp_c check (expected 30.0 ±5.0%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>initial_setup-chiller_service_configuration-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bda533ea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chiller issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try a change station and test again. If the problem persists, consult the TE.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63565151090061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. test station issue
+2. To check the WCK when Failed the 100C around.
+3. Temp Margin failed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. if temperature = 100 then change test station (retest), still fail and then report case to TE
+2 .Remove the plastic gasket of WCK.
+3. Re-curing, re-assembly, change new WCK </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -789,8 +859,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1131,872 +1202,921 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.375" style="1" customWidth="1"/>
-    <col min="2" max="3" width="14.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="87.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="151.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="58.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="86.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="106.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="39.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="36.625" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="13.375" style="2" customWidth="1"/>
+    <col min="2" max="3" width="14.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="87.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="151.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="58.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="86.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="106.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="39.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="28.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="36.625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="105">
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15">
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="25.2" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15">
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15">
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="22.8" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="165">
+      <c r="B12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="45">
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15">
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15">
+      <c r="A15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15">
+      <c r="A16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15">
+      <c r="B17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15">
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15">
+      <c r="B19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15">
+      <c r="B20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="45">
+      <c r="A21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15">
+      <c r="A22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15">
+      <c r="B23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="E23" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15">
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="G23" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="30">
+      <c r="A24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15">
+      <c r="A25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15">
-      <c r="A4" s="1" t="s">
+      <c r="G25" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15">
+      <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15">
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="15">
+      <c r="B27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15">
+      <c r="A28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15">
+      <c r="A29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="30">
+      <c r="A30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="30">
+      <c r="A31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="I31" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="75">
+      <c r="B32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="75">
+      <c r="A33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="45">
+      <c r="A34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="45">
+      <c r="A35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A36" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="25.2" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15">
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="22.8" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="D40" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="15">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="165">
-      <c r="B12" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="45">
-      <c r="B13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15">
-      <c r="B14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15">
-      <c r="A15" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15">
-      <c r="A16" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15">
-      <c r="B17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15">
-      <c r="B18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15">
-      <c r="B19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15">
-      <c r="A20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15">
-      <c r="A21" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15">
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15">
-      <c r="A23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15">
-      <c r="A25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15">
-      <c r="A26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15">
-      <c r="A27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15">
-      <c r="A28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15">
-      <c r="A29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="I29" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="30">
-      <c r="B30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="30">
-      <c r="A31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15">
-      <c r="A32" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15">
-      <c r="A33" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="45">
-      <c r="A34" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15">
-      <c r="A35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="1" t="s">
+      <c r="G40" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="I40" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>174</v>
-      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:J38">
+  <sortState ref="A2:J40">
     <sortCondition ref="D1"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="207">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -265,9 +265,6 @@
   </si>
   <si>
     <t>power_on-burn_os_if_needed_and_boot_os-ERROR-OutOfBandException</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test station issue? </t>
   </si>
   <si>
     <t>6a89dc65</t>
@@ -524,6 +521,246 @@
   </si>
   <si>
     <t>OE issue and OE team check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果是csm MPS29816 溫度過高, 通知ME
+re-curing 20min, 冷卻30min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mgmt_system_gpio-system_gpio_cplds_without_test_mode-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mnb_cpld_main_i2c__reg_BOARD_INT_STAT_REG_2__BIT_SMB_ALERT_L-DPL mnb_cpld_main_i2c, Register BOARD_INT_STAT_REG_2, bit SMB_ALERT_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change the test stataion, NV will remove this test item ??
+Retest
+(客人說是超過70度的原因 但檢查溫度沒有看出來 目前這項軟體認為不需要在FT測試這個 他們會討論移除這個項目)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fiber prbs issue
+TS2 MPS是0x70 (0x60~0x6C, 0x70, 0x71, 0x72) 但是test program卻要偵測0x6d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NV debugging, SA090057 has a special version test.
+Change station and  restest it again.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csm1_els_brd_cpld_reg_ft_prsnt_fnm__bit_fnm_prsnt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fnm module issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csm_monitoring_under_stress-get_els_pemi_laser_source_advanced-ERROR-ValueError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1.檢查是否op 沒有按/或機台問題
+2.檢查LED cable是否有受損 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(TS2#30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>567e5ee0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reset button issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_pb_pushed-Verify group_pb button pushed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(TS2#89)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csm_monitoring_under_stress-get_pemi_module_status-ERROR-ValueError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.Check the log and find the error windu. 
+2.Try to swap windu and test it again(OE team) 
+3. If the swap still fails and the connection ports are the same, please perform a hardware check.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>replace the windu and test again. (identify which windu is faulty), NV already resolve</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>verify fw burn comex-verify fw burn ERROR-TimeoutError</t>
+  </si>
+  <si>
+    <t>bec3c5db</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubProcess execution has exceeded timeout limit: 1200 sec​</t>
+  </si>
+  <si>
+    <t>windu issue, no els input power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_62065109160010 (BU#36)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Replace windu and check els input power</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA092538</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07d86568</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mgmt_cpu_monitoring_under_stress-read_cpu_temperatures-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cpu_temperature_core_0-checking CPU temperature core 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expected: 10 &lt;= x &lt;= 67, Received:100.0</t>
+  </si>
+  <si>
+    <t>f7340a0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset_button-reset_test-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reset_pushed-Verify reset button pushed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check if press the reset button or not</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Check if the reset button works correctly. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63765151110010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (localhost login:)|(ONIE: Rescue Mode ...)|(sonic login:)|(ONIE: OS Install Mode ...)
+Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (GNU GRUB)|(ONIE: Rescue Mode ...)|(Start PXE over)|(ONIE: OS Install Mode ...)|(Secure Boot Violation)|(Access granted)
+Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (Secure Boot Violation)|(ONIE: Rescue Mode ...)|(Access granted)|(Start PXE over)|(ONIE: OS Install Mode ...)|(GNU GRUB)
+Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (GNU GRUB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pcie_errors_check_before_stress-x86_pcie_capability_check-FAIL-MEASUREMENT;</t>
+  </si>
+  <si>
+    <t>mst_devices_Linkx-MST Linkx device presence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63265143660004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>03784b04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NV issue, follow instruction by Sharon
+(Before) step by step 5 times still Gen1x4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if temperature = 100 then change test station (retest)
+still fail and then report case to TE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. power light isn't on and minicom also no responds
+2. BMC no console.During disassembly of the MGMT, it was discovered that the MGMT-to-PBD cable was not fully seated.
+3. Check cable between IO board &amp; LED board damaged. Causing 3v3_aux shorted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Let hardware engineer check the power path, the cable connecting the MGMT module to the PDB was not fully seated.
+2. Change new cable and IO board 
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63665151890012 (TS2#77)
+SN_63265142450009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>setpoints_overall_flow_rate_sp_lpm-canonical setpoint overall_flow_rate_sp_lpm check (expected 30.0 ±5.0%)
+setpoints_overall_temperature_sp_c-canonical setpoint overall_temperature_sp_c check (expected 30.0 ±5.0%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>initial_setup-chiller_service_configuration-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bda533ea</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chiller issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try a change station and test again. If the problem persists, consult the TE.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63565151090061</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. test station issue
+2. To check the WCK when Failed the 100C around.
+3. Temp Margin failed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. if temperature = 100 then change test station (retest), still fail and then report case to TE
+2 .Remove the plastic gasket of WCK.
+3. Re-curing, re-assembly, change new WCK </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test station issue or other issues</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -537,243 +774,33 @@
 7.四個busbar拆開是否短路
 8.確認是否FBK鎖上以後短路
 9.BMC是否停在check point 15=&gt;換MGMT,DDR
-10.Console 是否有Failed to start ntpsec.service =&gt;測站問題</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果是csm MPS29816 溫度過高, 通知ME
-re-curing 20min, 冷卻30min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mgmt_system_gpio-system_gpio_cplds_without_test_mode-FAIL-MEASUREMENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mnb_cpld_main_i2c__reg_BOARD_INT_STAT_REG_2__BIT_SMB_ALERT_L-DPL mnb_cpld_main_i2c, Register BOARD_INT_STAT_REG_2, bit SMB_ALERT_L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>change the test stataion, NV will remove this test item ??
-Retest
-(客人說是超過70度的原因 但檢查溫度沒有看出來 目前這項軟體認為不需要在FT測試這個 他們會討論移除這個項目)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fiber prbs issue
-TS2 MPS是0x70 (0x60~0x6C, 0x70, 0x71, 0x72) 但是test program卻要偵測0x6d</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">NV debugging, SA090057 has a special version test.
-Change station and  restest it again.
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>csm1_els_brd_cpld_reg_ft_prsnt_fnm__bit_fnm_prsnt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>fnm module issue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>csm_monitoring_under_stress-get_els_pemi_laser_source_advanced-ERROR-ValueError</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>group_pb_button-group_pb_test-FAIL-MEASUREMENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1.檢查是否op 沒有按/或機台問題
-2.檢查LED cable是否有受損 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(TS2#30)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>567e5ee0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reset button issue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>group_pb_pushed-Verify group_pb button pushed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(TS2#89)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>csm_monitoring_under_stress-get_pemi_module_status-ERROR-ValueError</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.Check the log and find the error windu. 
-2.Try to swap windu and test it again(OE team) 
-3. If the swap still fails and the connection ports are the same, please perform a hardware check.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>replace the windu and test again. (identify which windu is faulty), NV already resolve</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>verify fw burn comex-verify fw burn ERROR-TimeoutError</t>
-  </si>
-  <si>
-    <t>bec3c5db</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SubProcess execution has exceeded timeout limit: 1200 sec​</t>
-  </si>
-  <si>
-    <t>windu issue, no els input power</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SN_62065109160010 (BU#36)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Replace windu and check els input power</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SA092538</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>07d86568</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mgmt_cpu_monitoring_under_stress-read_cpu_temperatures-FAIL-MEASUREMENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cpu_temperature_core_0-checking CPU temperature core 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Expected: 10 &lt;= x &lt;= 67, Received:100.0</t>
-  </si>
-  <si>
-    <t>f7340a0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>reset_button-reset_test-FAIL-MEASUREMENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>reset_pushed-Verify reset button pushed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>check if press the reset button or not</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Check if the reset button works correctly. </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SN_63765151110010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (localhost login:)|(ONIE: Rescue Mode ...)|(sonic login:)|(ONIE: OS Install Mode ...)
-Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (GNU GRUB)|(ONIE: Rescue Mode ...)|(Start PXE over)|(ONIE: OS Install Mode ...)|(Secure Boot Violation)|(Access granted)
-Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (Secure Boot Violation)|(ONIE: Rescue Mode ...)|(Access granted)|(Start PXE over)|(ONIE: OS Install Mode ...)|(GNU GRUB)
-Exceed timeout on command ControlKeys.USER_COMMAND without receiving expected-reply: (GNU GRUB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pcie_errors_check_before_stress-x86_pcie_capability_check-FAIL-MEASUREMENT;</t>
-  </si>
-  <si>
-    <t>mst_devices_Linkx-MST Linkx device presence</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SN_63265143660004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>03784b04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NV issue, follow instruction by Sharon
-(Before) step by step 5 times still Gen1x4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>if temperature = 100 then change test station (retest)
-still fail and then report case to TE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. power light isn't on and minicom also no responds
-2. BMC no console.During disassembly of the MGMT, it was discovered that the MGMT-to-PBD cable was not fully seated.
-3. Check cable between IO board &amp; LED board damaged. Causing 3v3_aux shorted</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Let hardware engineer check the power path, the cable connecting the MGMT module to the PDB was not fully seated.
-2. Change new cable and IO board 
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SN_63665151890012 (TS2#77)
-SN_63265142450009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>setpoints_overall_flow_rate_sp_lpm-canonical setpoint overall_flow_rate_sp_lpm check (expected 30.0 ±5.0%)
-setpoints_overall_temperature_sp_c-canonical setpoint overall_temperature_sp_c check (expected 30.0 ±5.0%)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>initial_setup-chiller_service_configuration-FAIL-MEASUREMENT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bda533ea</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>chiller issue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Try a change station and test again. If the problem persists, consult the TE.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SN_63565151090061</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. test station issue
-2. To check the WCK when Failed the 100C around.
-3. Temp Margin failed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1. if temperature = 100 then change test station (retest), still fail and then report case to TE
-2 .Remove the plastic gasket of WCK.
-3. Re-curing, re-assembly, change new WCK </t>
+10.Console 是否有Failed to start ntpsec.service =&gt;測站問題
+11.CPU console : ONIE: OS Install Mode ... =&gt; SSD沒有燒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7e52eba1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stress-run_stress-FAiL-MEASUREMENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cpo_collect_stress_integrated_iter_0-[meas,S,an,ei,li,oil,oli,fc,opm,eip,eocl,tp,prp,prb],[eocl:11.31,8,csm1_swb_maglan_asic_pcie,2,1,3,4,10,222.3,12.16,11.31,6.17,-2.81,7e-12],[eocl:11.34,8,csm1_swb_maglan_asic_pcie,2,1,3,5,10,222.3,12.13,11.34,6.02,-2.06,7e-12],[eocl:11.34,8,csm1_swb_maglan_asic_pcie,2,1,3,6,10,222.3,12.13,11.34,6.17,-2.14,7e-12],[eocl:11.27,8,csm1_swb_maglan_asic_pcie,2,1,3,7,10,222.3,12.2,11.27,6.17,-2.42,7e-12],[eocl:11.44,9,csm1_swb_maglan_asic_pcie,2,1,3,4,10,222.3,12.03,11.44,6.02,-2.81,8e-12],[eocl:11.44,9,csm1_swb_maglan_asic_pcie,2,1,3,5,10,222.3,12.03,11.44,6.02,-2.04,8e-12],[eocl:11.48,9,csm1_swb_maglan_asic_pcie,2,1,3,6,10,222.3,11.99,11.48,6.02,-2.09,8e-12],[eocl:11.38,9,csm1_swb_maglan_asic_pcie,2,1,3,7,10,222.3,12.09,11.38,6.02,-2.42,8e-12]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expected: row 4508, 6 &lt;= est_opt_channel_loss &lt;= 11, Received: est_opt_channel_loss=11.31
+--&gt; est_opt_channel_loss 超過規格上限 11 所以判定fail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OE team check, OE team will discuss with NV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SN_63565151080007</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1191,7 +1218,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1202,7 +1229,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.375" style="2" customWidth="1"/>
@@ -1252,28 +1279,28 @@
     </row>
     <row r="2" spans="1:10" ht="15">
       <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="105">
@@ -1281,22 +1308,22 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15">
@@ -1307,19 +1334,19 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="I4" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
@@ -1327,16 +1354,16 @@
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="25.2" customHeight="1">
@@ -1347,22 +1374,22 @@
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
@@ -1370,10 +1397,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
@@ -1381,19 +1408,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="22.8" customHeight="1">
@@ -1404,19 +1431,19 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15">
@@ -1427,19 +1454,19 @@
         <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15">
@@ -1450,42 +1477,42 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="165">
+    </row>
+    <row r="12" spans="1:10" ht="15">
       <c r="B12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45">
@@ -1493,16 +1520,16 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15">
@@ -1510,79 +1537,79 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15">
       <c r="A16" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15">
+    </row>
+    <row r="17" spans="1:9" ht="30">
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="F17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1590,13 +1617,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1604,42 +1631,42 @@
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="30">
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="I20" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="45">
+    </row>
+    <row r="21" spans="1:9" ht="15">
       <c r="A21" s="2" t="s">
         <v>17</v>
       </c>
@@ -1659,33 +1686,33 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15">
+    <row r="22" spans="1:9" ht="45">
       <c r="A22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="F22" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15">
+    </row>
+    <row r="23" spans="1:9" ht="60">
       <c r="B23" s="2" t="s">
         <v>23</v>
       </c>
@@ -1693,19 +1720,19 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="30">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -1713,22 +1740,22 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15">
+    </row>
+    <row r="25" spans="1:9" ht="30">
       <c r="A25" s="2" t="s">
         <v>22</v>
       </c>
@@ -1748,7 +1775,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>37</v>
@@ -1780,27 +1807,27 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15">
+    <row r="27" spans="1:9" ht="30">
       <c r="B27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1849,7 +1876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="30">
+    <row r="30" spans="1:9" ht="15">
       <c r="A30" s="2" t="s">
         <v>10</v>
       </c>
@@ -1872,7 +1899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="30">
+    <row r="31" spans="1:9" ht="15">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -1880,20 +1907,20 @@
         <v>11</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="G31" s="5"/>
       <c r="I31" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="75">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="180">
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -1907,16 +1934,16 @@
         <v>30</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="75">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15">
       <c r="A33" s="2" t="s">
         <v>17</v>
       </c>
@@ -1942,7 +1969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="45">
+    <row r="34" spans="1:9" ht="75">
       <c r="A34" s="2" t="s">
         <v>60</v>
       </c>
@@ -1959,16 +1986,16 @@
         <v>56</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="45">
+    </row>
+    <row r="35" spans="1:9" ht="15">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -1976,42 +2003,42 @@
         <v>11</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="14.25" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="14.25" customHeight="1">
@@ -2031,10 +2058,10 @@
         <v>52</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>53</v>
@@ -2042,51 +2069,51 @@
     </row>
     <row r="38" spans="1:9" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="G38" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="I38" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>182</v>
-      </c>
     </row>
     <row r="39" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>39</v>
+        <v>201</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>40</v>
+        <v>202</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>42</v>
+        <v>203</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>43</v>
+        <v>205</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="14.25" customHeight="1">
@@ -2097,26 +2124,49 @@
         <v>11</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="10" t="s">
+      <c r="G41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I41" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>170</v>
-      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:J40">
+  <sortState ref="A2:J41">
     <sortCondition ref="D1"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2128,6 +2178,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9191A586FB6BF428DA6CE3AFBC36CC2" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="93226386e723f3eec884d41ea14434fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9" xmlns:ns3="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e82c8add95932482acff31e34b978d29" ns2:_="" ns3:_="">
     <xsd:import namespace="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
@@ -2334,27 +2404,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE2B39F-8B1E-434F-AA50-190A864E0746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5"/>
+    <ds:schemaRef ds:uri="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0207815-F4C9-4B0B-8379-8B1E5F301B50}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B80DCE0-1924-49A6-B8F1-3B71CC84536B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2373,25 +2442,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0207815-F4C9-4B0B-8379-8B1E5F301B50}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE2B39F-8B1E-434F-AA50-190A864E0746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0debd8bc-6bf7-475a-9bb8-ad55401aa9d5"/>
-    <ds:schemaRef ds:uri="c98ac893-8ee2-44cc-8e6b-b75d78d71ec9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{44ccf059-af5d-4b92-932d-3690a1231c55}" enabled="1" method="Standard" siteId="{cb3d8dcd-2ed2-4bad-89a5-e0a7195fb643}" removed="0"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="227">
   <si>
     <t>TYPE(SAXXX)</t>
   </si>
@@ -414,17 +414,10 @@
     <t>562eSf9e</t>
   </si>
   <si>
-    <t>csm_system-gpio-systen_gpio_cplds-FAIL-MEASUREMENT</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
     <t>Check if fnm has been inserted</t>
   </si>
   <si>
     <t>ec7f6c67</t>
-  </si>
-  <si>
-    <t>csm_system-gpio-systen_gpio_cplds-ERROR-ValueError</t>
   </si>
   <si>
     <t>2ee565e6</t>
@@ -764,21 +757,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>change test station and retest it again.
-1.機器背後電源線插到底
-2.BMC是否有log
-3.如果BMC沒有開機=&gt;12V_AUX是否有短路
-4.LED燈是否全亮不會滅?(LEDcable受傷:TS2#8
-5.BMC是否完全沒有checkpoint=&gt;CSM重跑jtag
-6.12V_main是否短路(csm/mgmt LED燈號只有一半)
-7.四個busbar拆開是否短路
-8.確認是否FBK鎖上以後短路
-9.BMC是否停在check point 15=&gt;換MGMT,DDR
-10.Console 是否有Failed to start ntpsec.service =&gt;測站問題
-11.CPU console : ONIE: OS Install Mode ... =&gt; SSD沒有燒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7e52eba1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -801,6 +779,110 @@
   </si>
   <si>
     <t>SN_63565151080007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA090038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sbc storage usb-passmark-FAIL-MEASUREMENT</t>
+  </si>
+  <si>
+    <t>usb passmark_pass-Verify usb device passed passmark</t>
+  </si>
+  <si>
+    <t>2fdd016b</t>
+  </si>
+  <si>
+    <t>NV checking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Expected: x == True, Received: False</t>
+  </si>
+  <si>
+    <t>(TS3#28)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>change test station and retest it again.
+1.機器背後電源線插到底?
+2.BMC是否有log 
+3.如果BMC 沒有開機 =&gt; 12V_AUX是否正常? PDB to MGMT power cable沒插好(TS2#77 TS2#83)
+4.LED燈是否全亮不會滅? 3V3_AUX短路 (LED cable受傷: TS2#8/TS2#30/TS2#33)
+5.BMC有log, 但完全沒有check point =&gt; CSM重跑jtag (TS2#26, EVT#19)
+6.12V_main是否短路 (csm/mgmt LED燈號只有一半) (TS2#71, TS2#44:els 短路)
+7.四個busbar拆開是否短路
+8.確認哪個FBK鎖上以後短路/csm底部是否有雜質造成短路
+9.BMC有log, 停在check point 15 =&gt; 換MGMT, DDR (63465147980055)
+10.CPU console : Failed to start ntpsec.service =&gt; 測站問題 (TS2#69)
+11.CPU console : ONIE: OS Install Mode ... =&gt; SSD沒有燒 (TS1#51)
+12.Start PXE over IPv4.....目前沒有解 (63865158400049)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sbc_storage_ssd-write_psid_to_db-ERROR-TypeError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目前沒有解 (63865158400010)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unknown issue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csm_system-gpio-system_gpio_cplds-ERROR-ValueError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csm_system-gpio-system_gpio_cplds-FAIL-MEASUREMENT</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>發現pci_cr0 沒有抓到，ELS 16 根都不會亮燈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(TS3#16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">換PDB
+[之前]
+換上TS2#21 PDB 可以pass AOT (P)
+請必武重新點膠/重新link
+AOT(p) pass.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA092546</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>873c93ae</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>csml_asic_brd__pdb node_controller':'write i2c block' function failed: device=/dev/mst/192.168.10.20:23108,@dev@mstadev-i2c-6, i2c addr=0x60, addr width=1, reg addr=0xc7, size=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>power_on-validate_power_converter_dma_data-ERROR-Exception</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string indices must be integers</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a5c2bb86</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA091546</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -808,7 +890,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -859,6 +941,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -886,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -912,6 +1001,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1229,7 +1319,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.375" style="2" customWidth="1"/>
@@ -1238,7 +1328,7 @@
     <col min="5" max="5" width="151.625" style="2" customWidth="1"/>
     <col min="6" max="6" width="58.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="86.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="106.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.75" style="2" customWidth="1"/>
     <col min="9" max="9" width="39.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="28.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="36.625" style="2" customWidth="1"/>
@@ -1285,7 +1375,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>98</v>
@@ -1308,13 +1398,13 @@
         <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>102</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>36</v>
@@ -1334,19 +1424,19 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15">
@@ -1354,16 +1444,16 @@
         <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="25.2" customHeight="1">
@@ -1374,22 +1464,22 @@
         <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15">
@@ -1397,10 +1487,10 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15">
@@ -1411,16 +1501,16 @@
         <v>111</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="22.8" customHeight="1">
@@ -1466,7 +1556,7 @@
         <v>110</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15">
@@ -1497,22 +1587,22 @@
     </row>
     <row r="12" spans="1:10" ht="15">
       <c r="B12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="45">
@@ -1520,16 +1610,16 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15">
@@ -1537,16 +1627,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15">
@@ -1594,22 +1684,22 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="F17" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15">
@@ -1617,13 +1707,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15">
@@ -1631,16 +1721,16 @@
         <v>11</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="30">
@@ -1648,22 +1738,22 @@
         <v>11</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="I20" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15">
@@ -1688,28 +1778,28 @@
     </row>
     <row r="22" spans="1:9" ht="45">
       <c r="A22" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="F22" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60">
@@ -1720,16 +1810,16 @@
         <v>38</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15">
@@ -1775,7 +1865,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>37</v>
@@ -1812,22 +1902,22 @@
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15">
@@ -1920,7 +2010,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="180">
+    <row r="32" spans="1:9" ht="210">
       <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
@@ -1934,13 +2024,13 @@
         <v>30</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15">
@@ -1986,13 +2076,13 @@
         <v>56</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15">
@@ -2043,130 +2133,206 @@
     </row>
     <row r="37" spans="1:9" ht="14.25" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>17</v>
+        <v>220</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>221</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>149</v>
+        <v>223</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>53</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="14.25" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="G39" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="I39" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="14.25" customHeight="1">
-      <c r="B39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G39" s="2" t="s">
+    </row>
+    <row r="40" spans="1:9" ht="14.25" customHeight="1">
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="E40" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="I40" s="10"/>
     </row>
     <row r="41" spans="1:9" ht="14.25" customHeight="1">
       <c r="A41" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A42" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="E41" s="10" t="s">
+      <c r="G44" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I44" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>168</v>
-      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:J41">
+  <sortState ref="A2:J44">
     <sortCondition ref="D1"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2746,50 +2746,6 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SYSTEM_FT</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Test bin</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Test sub</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Aass</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Nooooooooo</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>無資料</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -2565,12 +2565,18 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>unknown issue</t>
+          <t>unknown issue (NV checking)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>目前沒有解 (63865158400010)</t>
+          <t>1.Reseat the MGMT SSD on connector J41,. Confirm it is fully in the MGMT socket.
+2.Boot and check nvme list and lspci for the SSD. You want a device, link up, expected speed and width.
+3.If it is still missing, measure SSD power at the socket (3.3 V rail up after power-on) and confirm PERST is released (not held low).
+4.Swap the SSD with a unit that passed sbc_storage_ssd on the same station.
+o Fail follows the SSD: that drive or its PSID label.
+o Fail stays on the board: socket, SSD power enable, or PCIe (REFCLK / PERST / lane). Do not start with the CPU.
+Repeat the swap on one more of the four. If both follow the SSD, hold the lot and check the SSD date code before more rework</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2752,6 +2752,50 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SYSTEM_FT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>a6d70386</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>query_fnm_linkup-linkup_polling_fnm-FAIL-MEASUREMENT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>linkup matrix_fnm-Failed:['port 65/0', 'port 65/1']</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>fnm issue ??</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>少見問題, 問題確認中</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SN_63865158370022</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -1607,7 +1607,13 @@
         <is>
           <t>change the test stataion, NV will remove this test item ??
 Retest
-(客人說是超過70度的原因 但檢查溫度沒有看出來 目前這項軟體認為不需要在FT測試這個 他們會討論移除這個項目)</t>
+(客人說是超過70度的原因 但檢查溫度沒有看出來 目前這項軟體認為不需要在FT測試這個 他們會討論移除這個項目)
+若出現此相關
+CPLD mnb cpld main i2c, Register 2obf, bit hscl vin pg
+CPLD mnb cpld main i2c,Register 2oDf, bit hsc2 vin pg
+CPLD mnb cpld main i2c, Register 20E0, bit hsc3 vin pg
+CPLD mnb cpld main i2c, Register 2Eo, bit hsc4 vin pg
+--&gt;NV Eliko : put it aside</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1617,7 +1623,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>SN_63665152170002</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2753,7 +2759,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
@@ -2794,7 +2804,11 @@
           <t>SN_63865158370022</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -2576,7 +2576,8 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1.Reseat the MGMT SSD on connector J41,. Confirm it is fully in the MGMT socket.
+          <t>SSD重燒就PASS(之前經驗)
+1.Reseat the MGMT SSD on connector J41,. Confirm it is fully in the MGMT socket.
 2.Boot and check nvme list and lspci for the SSD. You want a device, link up, expected speed and width.
 3.If it is still missing, measure SSD power at the socket (3.3 V rail up after power-on) and confirm PERST is released (not held low).
 4.Swap the SSD with a unit that passed sbc_storage_ssd on the same station.

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -2146,7 +2146,7 @@
 9.BMC有log, 停在check point 15 =&gt; 換MGMT, DDR (63465147980055)
 10.CPU console : Failed to start ntpsec.service =&gt; 測站問題 (TS2#69)
 11.CPU console : ONIE: OS Install Mode ... =&gt; SSD沒有燒 (TS1#51)
-12.Start PXE over IPv4.....目前沒有解 (63865158400049)</t>
+12.Start PXE over IPv4.....目前沒有解 (63865158400049)  --&gt;  Ahmad在解</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>(TS2#89)</t>
+          <t>(TS2#89)(SN_63865158400049)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>562eSf9e</t>
+          <t>562e5f9e</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2862,6 +2862,50 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SYSTEM_FT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>562e5f9e</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>csm_system_gpio-system_gpio_cplds-FAIL-MEASUREMENT</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>csm1_els_brd_cpld___reg_20E2___bit_asicl_fw_rst_-CPLD csm1_els_brd_cpld, Register 20E2, bit asicl_fw_rst</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>csm_system-gpio-system_gpio_cplds-FAIL-MEASUREMENT</t>
+          <t>csm_system_gpio-system_gpio_cplds-FAIL-MEASUREMENT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2863,7 +2863,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
@@ -2904,7 +2908,11 @@
           <t>無資料</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2914,6 +2914,76 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SYSTEM_FT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ad00de0f</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>power_on-update_pcie_dev-ERROR-ValueError</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PCIe issues not found: ['csm1_swb_maglan_asic_pcie: bdf=0000:02:00.0']</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>fuse issue</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>按照SOP, 先檢查fuse
+Dump FUSE prcedure:
+1. Power on the UUT and the Chiller:
+   cd /usr/flexfs/CSM_OPTICAL/tool/RD_TOOL
+   ./ono.sh
+   ./START_chiller.sh
+2. Use minicom to connect UUT.
+   minicom -b 115200
+3. Check the OPT-OS IP, assgin a IP if not assgined.
+   ifconfig eth0 192.168.10.101
+4. Copy fuse tool and MST scprit to UUT.
+   scp ./pcie_check/fuses root@192.168.10.101:/tmp
+   scp ./pcie_check/UUT_mst.sh root@192.168.10.101:/tmp
+5. Execute the MST script on UUT.
+   ssh root@192.168.10.101
+   /tmp/UUT_mst.sh
+6. Execute the dump fuse script on test station.
+   scp ./pcie_check/fuses /tmp &lt;-- the dump fuse script assume the fuse tool in /tmp
+   ssh root@127.0.0.1 &lt;-- get root privilege
+   ./pcie_check/STN_mst.sh &lt;UUT_IP&gt; &lt;UUT_NAME&gt;
+7. Collect the FUSE content on test station.
+   /tmp/spc6_fuse_dump_&lt;UUT_NMAE&gt;.log
+8. Power off the UUT and the Chiller:
+   cd /usr/log/RD_TOOL
+   ./offo.sh
+   ./STOP_chiller.sh
+NV有要求先重跑MGMT_JTAG, 然後讓回報NV連進來處理</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TS1#34</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -1551,9 +1551,9 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. if temperature = 100 then change test station (retest), still fail and then report case to TE
-2 .Remove the plastic gasket of WCK.
-3. Re-curing, re-assembly, change new WCK </t>
+          <t>1. if temperature = 100 then change test station (retest), still fail and then report case to TE
+2.Remove the plastic gasket of WCK.
+3. Re-curing, re-assembly, change new WCK</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2915,7 +2915,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>SYSTEM_FT</t>
@@ -2982,7 +2986,11 @@
           <t>TS1#34</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -2895,7 +2895,8 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>TS1#34 已宣告不處理放棄
+6M 6-3 同樣問題，待宣告</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2905,7 +2906,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>無資料</t>
+          <t>TS1#34(62865131330017)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2993,6 +2993,50 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MGMT_FT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>a62bfa07</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>memtestx86_group-memtestx86-ERROR-ValueError</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Expected exactly one MemTest86 report matching ....</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>the station issue</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>換站測</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SN_63865158400010</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -2843,7 +2843,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>少見問題, 問題確認中</t>
+          <t>少見問題, 問題確認中
+1. 檢查QSFP是否有插好
+2. QSFP換一根試試
+3. 請ME開蓋檢查,QSFP cable是否有插好(重插拔一次)
+4. 檢查QSFP cable 接頭是否有問題(過去有發生頂針歪了)
+      --&gt; 需換QSFP cable</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2994,7 +2999,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>MGMT_FT</t>
@@ -3035,7 +3044,11 @@
           <t>SN_63865158400010</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -2901,7 +2901,10 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>TS1#34 已宣告不處理放棄
-6M 6-3 同樣問題，待宣告</t>
+TS2#66 NV remote debug, 應該是NV 更新測試程式
+--&gt; 檢查log, NV bypass那個測項檢查
+6M 6-3 同樣問題，待宣告 
+ --&gt; NV remote debug, 等待測試版本更新</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2911,7 +2914,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TS1#34(62865131330017)</t>
+          <t>TS1#34(62865131330017),EVT#34, TS2#66, TS2#7,TS2#95</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3053,6 +3053,52 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MGMT_FT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>10b45df5</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>rtc-rtc_skew-FAIL-MEASUREMENT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>rtc_skew-Check RTC Skew</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>RTC issue - MGMT上的鈕扣電池相關</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>檢查 MGMT上的鈕扣電池
+1. 是否有鈕扣電池
+2. 是否沒電或者沒插好</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RCA.xlsx
+++ b/RCA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3054,7 +3054,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>MGMT_FT</t>
@@ -3097,7 +3101,58 @@
           <t>無資料</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>6762ec63</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>mst_devices_ELS-MST ELS device presence</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>link 不到ELS device</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1. 重插拔log中顯示link有問題WINDU
+2. SWAP WINDU
+3. 找一條ELS 那條cable試試
+4. 最終大招換ELS board</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>無資料</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
